--- a/cp-clarification-securitylabel/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/cp-clarification-securitylabel/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T15:16:01+00:00</t>
+    <t>2026-06-05T09:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
